--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0001T0006Z000C1N123_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0001T0006Z000C1N123_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>48.26930927671838</v>
+        <v>7.843762757466737</v>
       </c>
       <c r="D2" t="n">
-        <v>39.86788773549636</v>
+        <v>6.478531757018159</v>
       </c>
       <c r="E2" t="n">
-        <v>8.627239065076539</v>
+        <v>1.401926348074938</v>
       </c>
       <c r="F2" t="n">
-        <v>13.28497438448808</v>
+        <v>2.158808337479313</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>58.74407204928515</v>
+        <v>9.545911708008838</v>
       </c>
       <c r="D3" t="n">
-        <v>59.18659116918703</v>
+        <v>9.617821064992892</v>
       </c>
       <c r="E3" t="n">
-        <v>8.627239065076539</v>
+        <v>1.401926348074938</v>
       </c>
       <c r="F3" t="n">
-        <v>13.28497438448808</v>
+        <v>2.158808337479313</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>50.92097196296623</v>
+        <v>8.274657943982014</v>
       </c>
       <c r="D4" t="n">
-        <v>51.2756273449525</v>
+        <v>8.332289443554782</v>
       </c>
       <c r="E4" t="n">
-        <v>8.627239065076539</v>
+        <v>1.401926348074938</v>
       </c>
       <c r="F4" t="n">
-        <v>13.28497438448808</v>
+        <v>2.158808337479313</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>51.05787007763433</v>
+        <v>8.296903887615578</v>
       </c>
       <c r="D5" t="n">
-        <v>51.59938165463432</v>
+        <v>8.384899518878077</v>
       </c>
       <c r="E5" t="n">
-        <v>8.627239065076539</v>
+        <v>1.401926348074938</v>
       </c>
       <c r="F5" t="n">
-        <v>13.28497438448808</v>
+        <v>2.158808337479313</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>54.56282240193244</v>
+        <v>8.866458640314022</v>
       </c>
       <c r="D6" t="n">
-        <v>55.11347878127143</v>
+        <v>8.955940301956607</v>
       </c>
       <c r="E6" t="n">
-        <v>8.627239065076539</v>
+        <v>1.401926348074938</v>
       </c>
       <c r="F6" t="n">
-        <v>13.28497438448808</v>
+        <v>2.158808337479313</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>37.8841268832488</v>
+        <v>6.15617061852793</v>
       </c>
       <c r="D7" t="n">
-        <v>38.3956572384072</v>
+        <v>6.23929430124117</v>
       </c>
       <c r="E7" t="n">
-        <v>8.627239065076539</v>
+        <v>1.401926348074938</v>
       </c>
       <c r="F7" t="n">
-        <v>13.28497438448808</v>
+        <v>2.158808337479313</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>31.42177720453411</v>
+        <v>5.106038795736794</v>
       </c>
       <c r="D8" t="n">
-        <v>13.81400260728793</v>
+        <v>2.244775423684289</v>
       </c>
       <c r="E8" t="n">
-        <v>8.627239065076539</v>
+        <v>1.401926348074938</v>
       </c>
       <c r="F8" t="n">
-        <v>13.28497438448808</v>
+        <v>2.158808337479313</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>37.79052010544854</v>
+        <v>6.140959517135388</v>
       </c>
       <c r="D9" t="n">
-        <v>38.08101048585992</v>
+        <v>6.188164203952237</v>
       </c>
       <c r="E9" t="n">
-        <v>8.627239065076539</v>
+        <v>1.401926348074938</v>
       </c>
       <c r="F9" t="n">
-        <v>13.28497438448808</v>
+        <v>2.158808337479313</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>57.38408060877043</v>
+        <v>9.324913098925194</v>
       </c>
       <c r="D10" t="n">
-        <v>25.60416491299308</v>
+        <v>4.160676798361376</v>
       </c>
       <c r="E10" t="n">
-        <v>8.627239065076539</v>
+        <v>1.401926348074938</v>
       </c>
       <c r="F10" t="n">
-        <v>13.28497438448808</v>
+        <v>2.158808337479313</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>47.20180957819889</v>
+        <v>7.67029405645732</v>
       </c>
       <c r="D11" t="n">
-        <v>46.81811617946717</v>
+        <v>7.607943879163415</v>
       </c>
       <c r="E11" t="n">
-        <v>8.627239065076539</v>
+        <v>1.401926348074938</v>
       </c>
       <c r="F11" t="n">
-        <v>13.28497438448808</v>
+        <v>2.158808337479313</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
